--- a/Insiders/History/Summary.xlsx
+++ b/Insiders/History/Summary.xlsx
@@ -450,7 +450,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16:23:40</t>
+          <t>22:12:36</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Flipkart</t>
+          <t>flipkart</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="6">
@@ -484,7 +484,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chīrāla, Andhra Pradesh, IN</t>
+          <t>Vijayawada, Andhra Pradesh, IN</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2000</v>
+        <v>2028.57</v>
       </c>
     </row>
     <row r="4">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,9 +592,48 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2000</v>
+        <v>3500</v>
       </c>
       <c r="C2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Temple</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>400</v>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Makemytrip</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>usa</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C5" t="n">
         <v>1</v>
       </c>
     </row>
